--- a/astro-site/public/dl/kit-tareas-hotel/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -163,63 +165,63 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="10" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="11" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -579,15 +581,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -595,6 +598,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -623,9 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -647,8 +649,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -657,17 +676,17 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="32"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="40"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
-    <col customWidth="1" max="6" min="6" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1241,6 +1261,15 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/BONUS-02-calendario-anual-tareas.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>▸ Las 20 fechas y temporadas clave para F&amp;B en hoteles.</t>
+          <t>▸ Las 24 fechas y temporadas clave para F&amp;B en hoteles.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -678,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -699,7 +706,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AI Chef Pro · aichef.pro — 20 fechas clave para F&amp;B hotelero</t>
+          <t>AI Chef Pro · aichef.pro — 24 fechas clave para F&amp;B hotelero</t>
         </is>
       </c>
     </row>
@@ -820,22 +827,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Abril — Temporada media</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Grupos/congresos</t>
+          <t>19 Mar — Día del Padre</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Almuerzo familiar</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Preparar paquetes de coffee break y almuerzos de trabajo</t>
+          <t>Almuerzo de mediodía y brunch familiar; tarta por encargo y paquete con alojamiento</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>2 meses</t>
+          <t>3 semanas</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -846,22 +853,22 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Mayo — Bodas (inicio)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Banquetes pico</t>
+          <t>Abril — Temporada media</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Grupos/congresos</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Reservar personal extra, confirmar proveedores de boda</t>
+          <t>Preparar paquetes de coffee break y almuerzos de trabajo</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>6-12 meses</t>
+          <t>2 meses</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -872,17 +879,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Junio — Temporada alta</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Máx. ocupación</t>
+          <t>Abr-Jun — Comuniones</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Banquetes pico</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Ampliar horarios buffet, más show cooking, pool bar</t>
+          <t>Menú de adultos e infantil cerrados, salón, photocall y barra libre infantil; se contratan con 3-6 meses</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -898,22 +905,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Jul-Ago — Verano pleno</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>All-inclusive/resort</t>
+          <t>Mayo — Bodas (inicio)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Banquetes pico</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Menús refrescantes, helados, chiringuito, BBQ nocturna</t>
+          <t>Reservar personal extra, confirmar proveedores de boda</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>3 meses</t>
+          <t>6-12 meses</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -924,22 +931,22 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Septiembre — Vuelta congresos</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Corporativo fuerte</t>
+          <t>Junio — Temporada alta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Máx. ocupación</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Kick-offs, convenciones. Preparar paquetes de banquetes</t>
+          <t>Ampliar horarios buffet, más show cooking, pool bar</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>2 meses</t>
+          <t>3 meses</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -950,22 +957,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Octubre — Temporada de caza</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Menú especial</t>
+          <t>Jul-Ago — Verano pleno</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>All-inclusive/resort</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Incorporar caza y setas a carta y buffet</t>
+          <t>Menús refrescantes, helados, chiringuito, BBQ nocturna</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>4 semanas</t>
+          <t>3 meses</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -976,22 +983,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Octubre — Halloween</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Evento temático</t>
+          <t>Septiembre — Vuelta congresos</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Corporativo fuerte</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Buffet temático, cocktails especiales, decoración</t>
+          <t>Kick-offs, convenciones. Preparar paquetes de banquetes</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>4 semanas</t>
+          <t>2 meses</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1002,17 +1009,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Nov — Black Friday gastro</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Promoción</t>
+          <t>Octubre — Temporada de caza</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Menú especial</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Paquetes gastro: cena+alojamiento, brunch dominical</t>
+          <t>Incorporar caza y setas a carta y buffet</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1028,22 +1035,22 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Dic 1-20 — Cenas empresa</t>
+          <t>Octubre — Halloween</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Banquetes max</t>
+          <t>Evento temático</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Máxima demanda de banquetes corporativos del año</t>
+          <t>Buffet temático, cocktails especiales, decoración</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>3 meses</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1054,22 +1061,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>24 Dic — Nochebuena</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cena especial</t>
+          <t>1 Nov — Puente de Todos los Santos</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Ocupación alta</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Menú premium de Nochebuena. Reservas con antelación</t>
+          <t>Primer puente de la temporada baja: escapada nacional de 3 noches, buffet reforzado y menú de temporada (caza, setas)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>2 meses</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1080,22 +1087,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>25 Dic — Navidad</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Almuerzo familiar</t>
+          <t>Nov — Black Friday gastro</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Promoción</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Buffet de Navidad ampliado. Turrones y dulces</t>
+          <t>Paquetes gastro: cena+alojamiento, brunch dominical</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>2 meses</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1106,22 +1113,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>31 Dic — Nochevieja</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Gala + cotillón</t>
+          <t>6-8 Dic — Puente de la Constitución</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Ocupación alta</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Cena de gala + cotillón + barra libre. Personal máximo</t>
+          <t>Tres días seguidos con cenas de empresa adelantadas: buffet reforzado, salones dobles y personal extra cerrado ANTES del puente</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>3 meses</t>
+          <t>6 semanas</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1132,22 +1139,22 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Todo el año — Brunch dominical</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Outlet fijo</t>
+          <t>Dic 1-20 — Cenas empresa</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Banquetes max</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Brunch premium con champagne, huevos benedict, show</t>
+          <t>Máxima demanda de banquetes corporativos del año</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>3 meses</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1158,22 +1165,22 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Todo el año — Amenities VIP</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Room service</t>
+          <t>24 Dic — Nochebuena</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Cena especial</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Welcome drinks, fruit baskets, chocolate turndown</t>
+          <t>Menú premium de Nochebuena. Reservas con antelación</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Stock mensual</t>
+          <t>2 meses</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1184,22 +1191,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Todo el año — Grupos MICE</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>25 Dic — Navidad</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Almuerzo familiar</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Coffee breaks, almuerzos de trabajo, cenas de gala</t>
+          <t>Buffet de Navidad ampliado. Turrones y dulces</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>1-3 meses</t>
+          <t>2 meses</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1210,22 +1217,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Festivos locales</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>Variable</t>
+          <t>31 Dic — Nochevieja</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Gala + cotillón</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Menú especial según festividad local. Consultar calendario</t>
+          <t>Cena de gala + cotillón + barra libre. Personal máximo</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>4-6 semanas</t>
+          <t>3 meses</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1236,25 +1243,129 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>Todo el año — Brunch dominical</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Outlet fijo</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Brunch premium con champagne, huevos benedict, show</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Todo el año — Amenities VIP</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Room service</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Welcome drinks, fruit baskets, chocolate turndown</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Stock mensual</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Todo el año — Grupos MICE</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Coffee breaks, almuerzos de trabajo, cenas de gala</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Festivos locales</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Menú especial según festividad local. Consultar calendario</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>4-6 semanas</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>Inspección sanidad</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>Obligatorio</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Preparar toda documentación APPCC, temperaturas, formación</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Permanente</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
